--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575920725</v>
+        <v>46157.93121100737</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93121100737</v>
+        <v>46157.93186755401</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93186755401</v>
+        <v>46157.93407291015</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93407291015</v>
+        <v>46157.93725420139</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93725420139</v>
+        <v>46158.2822289348</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2822289348</v>
+        <v>46158.29712235552</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29712235552</v>
+        <v>46158.29823018864</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29823018864</v>
+        <v>46158.33393909092</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393909092</v>
+        <v>46158.36863661253</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863661253</v>
+        <v>46158.37294659601</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
